--- a/Dispersão KM por Motorista.xlsx
+++ b/Dispersão KM por Motorista.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export" sheetId="1" r:id="R0963e7c0761c46bd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export" sheetId="1" r:id="R07ca969c74884015"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -99,7 +99,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.22186495176848875</x:v>
+        <x:v>0.33404947160608534</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -130,6 +130,19 @@
     </x:row>
     <x:row>
       <x:c s="8">
+        <x:v>1265</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>APARECIDO  LIMA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.13177750482540795</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
         <x:v>10</x:v>
       </x:c>
       <x:c t="inlineStr">
@@ -151,7 +164,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.15390847434087185</x:v>
+        <x:v>0.12705549054628329</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -169,6 +182,32 @@
     </x:row>
     <x:row>
       <x:c s="8">
+        <x:v>694</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>DILSON  FRANCA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.43706640237859262</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>294</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>EDENILSON  FAZAN</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.1718983557548579</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
         <x:v>118</x:v>
       </x:c>
       <x:c t="inlineStr">
@@ -203,7 +242,20 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.46249832282302417</x:v>
+        <x:v>0.40241879542781311</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>319</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>EVERTON  ARAUJO</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.388235294117647</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -216,7 +268,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.41816966027081737</x:v>
+        <x:v>0.3627471810915166</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -242,7 +294,20 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.17338273892234057</x:v>
+        <x:v>0.20692611006343231</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>520</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>GEOVANE  SILVA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.018990273274664293</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -255,7 +320,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.11487027735107591</x:v>
+        <x:v>0.19296604105894666</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -281,7 +346,20 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.17507720164200746</x:v>
+        <x:v>0.18729351417144824</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>559</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>IGOR  ARAUJO</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.18893642423639445</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -320,7 +398,20 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.35085276299972645</x:v>
+        <x:v>0.32228038012239746</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>553</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>JHONATAN  RODRIGUES</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.46801051709027175</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -333,7 +424,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.1787085159142634</x:v>
+        <x:v>0.16312713384642086</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -351,6 +442,19 @@
     </x:row>
     <x:row>
       <x:c s="8">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>JORGE  LIMA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.15929239038870402</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
         <x:v>323</x:v>
       </x:c>
       <x:c t="inlineStr">
@@ -364,6 +468,32 @@
     </x:row>
     <x:row>
       <x:c s="8">
+        <x:v>604</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>JOSE  RODRIGUES</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.066721021877972575</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>246</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>JOSE  SOUZA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.37777296159264351</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
         <x:v>453</x:v>
       </x:c>
       <x:c t="inlineStr">
@@ -424,7 +554,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.24234912653751728</x:v>
+        <x:v>0.21016866556569314</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -489,7 +619,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.21293609794069779</x:v>
+        <x:v>0.23599182442907796</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -502,7 +632,20 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.12342259156663582</x:v>
+        <x:v>0.11427034503957567</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>341</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>NILDO  TONIAZZO</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.11943149690532584</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -520,6 +663,19 @@
     </x:row>
     <x:row>
       <x:c s="8">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>PODALIRIO  NATES</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.36116876896056205</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
         <x:v>16</x:v>
       </x:c>
       <x:c t="inlineStr">
@@ -528,7 +684,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.8369095292172215</x:v>
+        <x:v>0.53267663214919625</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -546,6 +702,19 @@
     </x:row>
     <x:row>
       <x:c s="8">
+        <x:v>320</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>RENAN  ARAUJO</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.10073736141318768</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
         <x:v>287</x:v>
       </x:c>
       <x:c t="inlineStr">
@@ -554,7 +723,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.13083680658769348</x:v>
+        <x:v>0.16335386406665053</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -567,7 +736,33 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.48863719134678418</x:v>
+        <x:v>0.44319699928064948</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>348</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>STEFANES  TERNOSKI</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.96850393700787407</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>328</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>TENISON  RODRIGUES</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.025923330997897898</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -594,6 +789,19 @@
       </x:c>
       <x:c s="9">
         <x:v>0.741620868488273</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>352</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>VINALDO  SOUZA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.40717203812982294</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -630,7 +838,7 @@
       </x:c>
       <x:c s="1"/>
       <x:c s="10">
-        <x:v>0.25160836450567992</x:v>
+        <x:v>0.24598136659993819</x:v>
       </x:c>
     </x:row>
     <x:row/>
@@ -640,9 +848,8 @@
           <x:t>Filtros aplicados:
 Mapas KM maior que 0
 Revenda é GranDourados
-Frota é Padronizada
 Ano é 2026
-Date é igual a ou está depois de 01/09/2026 e está antes de 11/09/2026
+Date é igual a ou está depois de 01/09/2026 e está antes de 13/09/2026
 Taxa de Dispersão é Até 100%
 Check Dispersão KM é Sim
 Tipo Dispersão KM é Positiva

--- a/Dispersão KM por Motorista.xlsx
+++ b/Dispersão KM por Motorista.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export" sheetId="1" r:id="R6ae2518258dd4969"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export" sheetId="1" r:id="R47b74b8bdcf54aed"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -78,6 +78,19 @@
     </x:row>
     <x:row>
       <x:c s="8">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>ADEMILSON  PANTALEAO</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.32113821138211374</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
         <x:v>248</x:v>
       </x:c>
       <x:c t="inlineStr">
@@ -86,7 +99,20 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.33664028039742755</x:v>
+        <x:v>0.33404947160608534</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>284</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>ADRIEL  CORONEL</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.16006692693809255</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -99,7 +125,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.030927835051546504</x:v>
+        <x:v>0.076830006049606769</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -125,7 +151,33 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.17694942848421125</x:v>
+        <x:v>0.18160460404412393</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CLAUDEMIR  GOMES</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.11367127496159757</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>ELIZEU  SILVA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.17306419589675714</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -138,7 +190,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.14088617670469628</x:v>
+        <x:v>0.22826386972122537</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -164,7 +216,20 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.15564809994794393</x:v>
+        <x:v>0.3627471810915166</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>544</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>GENIVAL  SILVA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.85036202735317779</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -177,7 +242,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.2595512298240592</x:v>
+        <x:v>0.20692611006343231</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -203,7 +268,20 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.40414362528987535</x:v>
+        <x:v>0.19296604105894666</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>GUTIER  FLORES</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.23665712054152577</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -216,7 +294,33 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.30507529280535417</x:v>
+        <x:v>0.18729351417144824</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>350</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>ISMAEL  SIQUEIRA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.18034586878945924</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>JACKES  SOUZA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.27462340672074159</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -229,7 +333,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.44681892047738048</x:v>
+        <x:v>0.32228038012239746</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -242,7 +346,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.15614389478660762</x:v>
+        <x:v>0.16283756549778294</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -255,7 +359,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.0042527027719425625</x:v>
+        <x:v>0.052631578947368363</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -268,7 +372,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.11771202254465152</x:v>
+        <x:v>0.14937962631920443</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -286,6 +390,19 @@
     </x:row>
     <x:row>
       <x:c s="8">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>JUNIOR  SILVA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.346690508076402</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
         <x:v>313</x:v>
       </x:c>
       <x:c t="inlineStr">
@@ -294,7 +411,20 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.24038700074423214</x:v>
+        <x:v>0.36676499508357918</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>LEONEL  COVA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.12639071245940148</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -307,7 +437,59 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.22675303007998426</x:v>
+        <x:v>0.21016866556569314</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>285</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MARCELO  ZENATTI</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.49903288201160545</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>314</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MARCOS  TEIXEIRA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.87441424554826619</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>732</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MARIO  MELCHIOR</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.088763049730794963</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MATHEUS  COSTA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.24698310539018498</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -320,7 +502,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.23527409906811392</x:v>
+        <x:v>0.23712000292701241</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -338,6 +520,19 @@
     </x:row>
     <x:row>
       <x:c s="8">
+        <x:v>268</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>NIY  OLIVEIRA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.32108513318381515</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
         <x:v>16</x:v>
       </x:c>
       <x:c t="inlineStr">
@@ -346,7 +541,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.34530944521008955</x:v>
+        <x:v>0.49157051560105236</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -359,7 +554,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.89537528430629276</x:v>
+        <x:v>0.74441395531164267</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -372,7 +567,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.13610442276010648</x:v>
+        <x:v>0.16335386406665053</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -385,7 +580,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.33437990580847732</x:v>
+        <x:v>0.44319699928064948</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -398,7 +593,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.16640746500777603</x:v>
+        <x:v>0.14454218312674927</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -412,6 +607,19 @@
       </x:c>
       <x:c s="9">
         <x:v>0.45465591143811812</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>302</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>WELLINGTON  BERRETA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.34911242603550297</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -435,7 +643,7 @@
       </x:c>
       <x:c s="1"/>
       <x:c s="10">
-        <x:v>0.24916477506978008</x:v>
+        <x:v>0.2519692170796155</x:v>
       </x:c>
     </x:row>
     <x:row/>
@@ -447,7 +655,7 @@
 Revenda é GranDourados
 Frota não é Spot
 Ano é 2026
-Date é igual a ou está depois de 07/09/2026 e está antes de 15/09/2026
+Date é igual a ou está depois de 01/09/2026 e está antes de 15/09/2026
 Taxa de Dispersão é Até 100%
 Check Dispersão KM é Sim
 Tipo Dispersão KM é Positiva

--- a/Dispersão KM por Motorista.xlsx
+++ b/Dispersão KM por Motorista.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export" sheetId="1" r:id="R47b74b8bdcf54aed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export" sheetId="1" r:id="Raaa9274fcae64c95"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -130,6 +130,19 @@
     </x:row>
     <x:row>
       <x:c s="8">
+        <x:v>316</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>ANDERSON  MELO</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.039984673910068658</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
         <x:v>10</x:v>
       </x:c>
       <x:c t="inlineStr">
@@ -242,7 +255,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.20692611006343231</x:v>
+        <x:v>0.19876309444346085</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -255,7 +268,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.018990273274664293</x:v>
+        <x:v>0.22834645669291342</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -268,7 +281,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.19296604105894666</x:v>
+        <x:v>0.17968261191058543</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -333,7 +346,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.32228038012239746</x:v>
+        <x:v>0.28738033072236724</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -372,7 +385,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.14937962631920443</x:v>
+        <x:v>0.15270555736106606</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -385,7 +398,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.30344108446298224</x:v>
+        <x:v>0.21876904326630098</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -502,7 +515,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.23712000292701241</x:v>
+        <x:v>0.21756617030457481</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -593,7 +606,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.14454218312674927</x:v>
+        <x:v>0.132992399627045</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -607,6 +620,19 @@
       </x:c>
       <x:c s="9">
         <x:v>0.45465591143811812</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>352</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>VINALDO  SOUZA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.40717203812982294</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -643,7 +669,7 @@
       </x:c>
       <x:c s="1"/>
       <x:c s="10">
-        <x:v>0.2519692170796155</x:v>
+        <x:v>0.24346090605537651</x:v>
       </x:c>
     </x:row>
     <x:row/>
@@ -653,10 +679,10 @@
           <x:t>Filtros aplicados:
 Mapas KM maior que 0
 Revenda é GranDourados
-Frota não é Spot
 Ano é 2026
-Date é igual a ou está depois de 01/09/2026 e está antes de 15/09/2026
+Date é igual a ou está depois de 01/09/2026 e está antes de 16/09/2026
 Taxa de Dispersão é Até 100%
+Supervisor não é 3
 Check Dispersão KM é Sim
 Tipo Dispersão KM é Positiva
 Meta Dispersão KM é 20

--- a/Dispersão KM por Motorista.xlsx
+++ b/Dispersão KM por Motorista.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export" sheetId="1" r:id="Raaa9274fcae64c95"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export" sheetId="1" r:id="R042a06ccce0b4fe1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -190,7 +190,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.17306419589675714</x:v>
+        <x:v>0.12635267329140354</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -216,7 +216,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.40241879542781311</x:v>
+        <x:v>0.36176096212087971</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -307,7 +307,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.18729351417144824</x:v>
+        <x:v>0.2134879725085912</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -346,7 +346,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.28738033072236724</x:v>
+        <x:v>0.24879532761283274</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -359,7 +359,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.16283756549778294</x:v>
+        <x:v>0.1968579573624194</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -372,7 +372,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.052631578947368363</x:v>
+        <x:v>0.05024939358665037</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -450,7 +450,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.21016866556569314</x:v>
+        <x:v>0.26771631556482789</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -515,7 +515,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.21756617030457481</x:v>
+        <x:v>0.20668000525754682</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -528,7 +528,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.11427034503957567</x:v>
+        <x:v>0.17135351621377182</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -567,7 +567,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.74441395531164267</x:v>
+        <x:v>0.35674600452705962</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -585,6 +585,19 @@
     </x:row>
     <x:row>
       <x:c s="8">
+        <x:v>349</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>RODRIGO  GONCALVES</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.16834838024429111</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
         <x:v>288</x:v>
       </x:c>
       <x:c t="inlineStr">
@@ -620,19 +633,6 @@
       </x:c>
       <x:c s="9">
         <x:v>0.45465591143811812</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="8">
-        <x:v>352</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>VINALDO  SOUZA</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.40717203812982294</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -669,7 +669,7 @@
       </x:c>
       <x:c s="1"/>
       <x:c s="10">
-        <x:v>0.24346090605537651</x:v>
+        <x:v>0.24425682930223003</x:v>
       </x:c>
     </x:row>
     <x:row/>
@@ -679,10 +679,11 @@
           <x:t>Filtros aplicados:
 Mapas KM maior que 0
 Revenda é GranDourados
+Frota não é Spot
 Ano é 2026
-Date é igual a ou está depois de 01/09/2026 e está antes de 16/09/2026
+Date é igual a ou está depois de 01/09/2026 e está antes de 17/09/2026
 Taxa de Dispersão é Até 100%
-Supervisor não é 3
+Supervisor é 2 ou 1
 Check Dispersão KM é Sim
 Tipo Dispersão KM é Positiva
 Meta Dispersão KM é 20

--- a/Dispersão KM por Motorista.xlsx
+++ b/Dispersão KM por Motorista.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export" sheetId="1" r:id="R042a06ccce0b4fe1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export" sheetId="1" r:id="R15e4dd4b36c440f0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -164,7 +164,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.18160460404412393</x:v>
+        <x:v>0.19365555780442412</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -255,7 +255,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.19876309444346085</x:v>
+        <x:v>0.18394682624780367</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -281,7 +281,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.17968261191058543</x:v>
+        <x:v>0.17221369164967282</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -385,7 +385,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.15270555736106606</x:v>
+        <x:v>0.26468304449107039</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -489,7 +489,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.088763049730794963</x:v>
+        <x:v>0.0945050493359183</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -515,7 +515,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.20668000525754682</x:v>
+        <x:v>0.2488976414500077</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -528,7 +528,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.17135351621377182</x:v>
+        <x:v>0.15000371235057774</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -593,7 +593,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.16834838024429111</x:v>
+        <x:v>0.10747545935061664</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -632,7 +632,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.45465591143811812</x:v>
+        <x:v>0.40858752671459109</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -669,7 +669,7 @@
       </x:c>
       <x:c s="1"/>
       <x:c s="10">
-        <x:v>0.24425682930223003</x:v>
+        <x:v>0.24713633769192067</x:v>
       </x:c>
     </x:row>
     <x:row/>
@@ -681,9 +681,8 @@
 Revenda é GranDourados
 Frota não é Spot
 Ano é 2026
-Date é igual a ou está depois de 01/09/2026 e está antes de 17/09/2026
+Date é igual a ou está depois de 01/09/2026 e está antes de 18/09/2026
 Taxa de Dispersão é Até 100%
-Supervisor é 2 ou 1
 Check Dispersão KM é Sim
 Tipo Dispersão KM é Positiva
 Meta Dispersão KM é 20

--- a/Dispersão KM por Motorista.xlsx
+++ b/Dispersão KM por Motorista.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export" sheetId="1" r:id="R15e4dd4b36c440f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export" sheetId="1" r:id="R99e07c5187dd4912"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -164,7 +164,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.19365555780442412</x:v>
+        <x:v>0.18210987126693579</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -190,7 +190,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.12635267329140354</x:v>
+        <x:v>0.20315951035076552</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -216,7 +216,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.36176096212087971</x:v>
+        <x:v>0.30525597851570829</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -229,7 +229,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.3627471810915166</x:v>
+        <x:v>0.33288239592706903</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -242,7 +242,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.85036202735317779</x:v>
+        <x:v>0.47377546597312525</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -255,7 +255,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.18394682624780367</x:v>
+        <x:v>0.15497558842168213</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -281,7 +281,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.17221369164967282</x:v>
+        <x:v>0.15201602804908587</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -346,7 +346,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.24879532761283274</x:v>
+        <x:v>0.33463035019455245</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -372,7 +372,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.05024939358665037</x:v>
+        <x:v>0.041487302307864793</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -450,7 +450,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.26771631556482789</x:v>
+        <x:v>0.23607097953483125</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -489,7 +489,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.0945050493359183</x:v>
+        <x:v>0.13311635731040283</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -515,7 +515,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.2488976414500077</x:v>
+        <x:v>0.24247466343972168</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -528,7 +528,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.15000371235057774</x:v>
+        <x:v>0.17808757117612406</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -541,7 +541,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.32108513318381515</x:v>
+        <x:v>0.39616055846422338</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -580,7 +580,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.16335386406665053</x:v>
+        <x:v>0.24197649755464745</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -593,7 +593,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.10747545935061664</x:v>
+        <x:v>0.12016293279022405</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -606,7 +606,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.44319699928064948</x:v>
+        <x:v>0.49712276984566484</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -619,7 +619,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.132992399627045</x:v>
+        <x:v>0.13490224432104414</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -632,7 +632,20 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.40858752671459109</x:v>
+        <x:v>0.361107378040586</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>352</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>VINALDO  SOUZA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.40717203812982294</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -669,7 +682,7 @@
       </x:c>
       <x:c s="1"/>
       <x:c s="10">
-        <x:v>0.24713633769192067</x:v>
+        <x:v>0.25281025449281191</x:v>
       </x:c>
     </x:row>
     <x:row/>
@@ -679,10 +692,10 @@
           <x:t>Filtros aplicados:
 Mapas KM maior que 0
 Revenda é GranDourados
-Frota não é Spot
 Ano é 2026
-Date é igual a ou está depois de 01/09/2026 e está antes de 18/09/2026
+Date é igual a ou está depois de 01/09/2026 e está antes de 22/09/2026
 Taxa de Dispersão é Até 100%
+Supervisor não é 3
 Check Dispersão KM é Sim
 Tipo Dispersão KM é Positiva
 Meta Dispersão KM é 20

--- a/Dispersão KM por Motorista.xlsx
+++ b/Dispersão KM por Motorista.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export" sheetId="1" r:id="R99e07c5187dd4912"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export" sheetId="1" r:id="Rfa2c0106491d44ef"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -99,7 +99,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.33404947160608534</x:v>
+        <x:v>0.64886607907445493</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -112,7 +112,33 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.16006692693809255</x:v>
+        <x:v>0.75220862958751433</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>ALEXANDRE  CACERES</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.43596644429810749</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>665</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>ALEXANDRE  COSTA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.77370343907141037</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -125,7 +151,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.076830006049606769</x:v>
+        <x:v>0.7957138970246953</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -138,7 +164,20 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.039984673910068658</x:v>
+        <x:v>0.48618027392457908</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>BRUCE  SANTOS</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.97062926793450321</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -151,7 +190,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.51561079114883279</x:v>
+        <x:v>0.74481034049647166</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -164,7 +203,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.18210987126693579</x:v>
+        <x:v>0.35677548201867615</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -177,7 +216,33 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.11367127496159757</x:v>
+        <x:v>0.6463437617791179</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>336</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>ELIAS  SILVA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.36982813494589428</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>ELIZEU  SANTOS</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.88936436697630716</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -190,7 +255,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.20315951035076552</x:v>
+        <x:v>0.38711355562175709</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -203,7 +268,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.22826386972122537</x:v>
+        <x:v>0.4405329880043618</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -216,7 +281,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.30525597851570829</x:v>
+        <x:v>0.25059612163910749</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -229,7 +294,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.33288239592706903</x:v>
+        <x:v>0.29027410645810536</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -242,7 +307,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.47377546597312525</x:v>
+        <x:v>0.68217516889069252</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -255,7 +320,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.15497558842168213</x:v>
+        <x:v>0.37100375520146134</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -268,7 +333,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.22834645669291342</x:v>
+        <x:v>0.69737405451691181</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -281,7 +346,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.15201602804908587</x:v>
+        <x:v>0.24095200136016137</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -294,7 +359,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.23665712054152577</x:v>
+        <x:v>0.46182594767752261</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -307,7 +372,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.2134879725085912</x:v>
+        <x:v>0.28532942220849877</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -320,7 +385,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.18034586878945924</x:v>
+        <x:v>0.37549363756033349</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -333,7 +398,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.27462340672074159</x:v>
+        <x:v>0.77948065931296751</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -346,7 +411,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.33463035019455245</x:v>
+        <x:v>0.39014424937853209</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -359,7 +424,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.1968579573624194</x:v>
+        <x:v>0.52386376034850279</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -372,7 +437,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.041487302307864793</x:v>
+        <x:v>0.29755947581593967</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -385,7 +450,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.26468304449107039</x:v>
+        <x:v>0.40199694258255558</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -398,7 +463,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.21876904326630098</x:v>
+        <x:v>0.690720352312048</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -424,7 +489,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.36676499508357918</x:v>
+        <x:v>0.58253843564134211</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -437,7 +502,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.12639071245940148</x:v>
+        <x:v>0.67583235911150963</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -450,7 +515,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.23607097953483125</x:v>
+        <x:v>0.28262067273107849</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -463,7 +528,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.49903288201160545</x:v>
+        <x:v>0.40523721156910164</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -476,7 +541,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.87441424554826619</x:v>
+        <x:v>0.87623550490220481</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -489,7 +554,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.13311635731040283</x:v>
+        <x:v>0.1834284449079</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -502,7 +567,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.24698310539018498</x:v>
+        <x:v>0.604849046826847</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -515,7 +580,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.24247466343972168</x:v>
+        <x:v>0.2285217496943881</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -528,7 +593,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.17808757117612406</x:v>
+        <x:v>0.43064658258522881</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -541,7 +606,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.39616055846422338</x:v>
+        <x:v>0.61433146044052012</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -554,7 +619,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.49157051560105236</x:v>
+        <x:v>0.74352765975172863</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -567,7 +632,20 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.35674600452705962</x:v>
+        <x:v>0.52536607299955018</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>261</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>RENATO  OJEDA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.91528631423370155</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -580,7 +658,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.24197649755464745</x:v>
+        <x:v>0.40785424686464489</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -593,7 +671,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.12016293279022405</x:v>
+        <x:v>0.39698806148724208</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -606,7 +684,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.49712276984566484</x:v>
+        <x:v>0.64446387568751007</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -619,7 +697,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.13490224432104414</x:v>
+        <x:v>0.29938333908536241</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -632,20 +710,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.361107378040586</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="8">
-        <x:v>352</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>VINALDO  SOUZA</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.40717203812982294</x:v>
+        <x:v>0.41656311978780858</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -658,7 +723,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.34911242603550297</x:v>
+        <x:v>0.73625154766817991</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -671,7 +736,20 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.22494432071269488</x:v>
+        <x:v>0.62999452654625077</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>714</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>YOSMER  FAJARDO</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.52090351797647316</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -682,7 +760,7 @@
       </x:c>
       <x:c s="1"/>
       <x:c s="10">
-        <x:v>0.25281025449281191</x:v>
+        <x:v>0.47478552697368692</x:v>
       </x:c>
     </x:row>
     <x:row/>
@@ -692,12 +770,11 @@
           <x:t>Filtros aplicados:
 Mapas KM maior que 0
 Revenda é GranDourados
+Frota não é Spot
 Ano é 2026
-Date é igual a ou está depois de 01/09/2026 e está antes de 22/09/2026
+Date é igual a ou está depois de 01/09/2026 e está antes de 26/09/2026
 Taxa de Dispersão é Até 100%
-Supervisor não é 3
 Check Dispersão KM é Sim
-Tipo Dispersão KM é Positiva
 Meta Dispersão KM é 20
 Tipo Mapa é Recarga Rota ou Rota
 Check Status Mapa é Fechado</x:t>
